--- a/Restruk_Data.xlsx
+++ b/Restruk_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJEK DASHBOARD MONITORING\Dashboard_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B641C4D-C5B7-4C2F-98A7-F95FF6149397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335B7998-53ED-4C4C-8642-FD852C920894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{148A6939-ADF4-475D-9E15-4D85AB9B8990}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{148A6939-ADF4-475D-9E15-4D85AB9B8990}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="23">
   <si>
     <t>UNIT</t>
   </si>
@@ -104,7 +104,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.000%"/>
     <numFmt numFmtId="165" formatCode="#,##0;[Red]#,##0"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -176,7 +176,7 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -199,7 +199,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
@@ -516,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBC49A10-5EE6-42C0-A039-D887B0D53534}">
-  <dimension ref="A1:D417"/>
+  <dimension ref="A1:D418"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -4348,21 +4348,21 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" s="8">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B274" s="8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C274" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D274" s="13">
-        <v>8.11</v>
+        <v>7</v>
+      </c>
+      <c r="D274" s="7">
+        <v>500000</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B275" s="8" t="s">
         <v>15</v>
@@ -4371,12 +4371,12 @@
         <v>16</v>
       </c>
       <c r="D275" s="13">
-        <v>8.2899999999999991</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B276" s="8" t="s">
         <v>15</v>
@@ -4385,12 +4385,12 @@
         <v>16</v>
       </c>
       <c r="D276" s="13">
-        <v>8.3000000000000007</v>
+        <v>8.2899999999999991</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B277" s="8" t="s">
         <v>15</v>
@@ -4399,12 +4399,12 @@
         <v>16</v>
       </c>
       <c r="D277" s="13">
-        <v>8.33</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B278" s="8" t="s">
         <v>15</v>
@@ -4413,12 +4413,12 @@
         <v>16</v>
       </c>
       <c r="D278" s="13">
-        <v>8.1999999999999993</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B279" s="8" t="s">
         <v>15</v>
@@ -4427,12 +4427,12 @@
         <v>16</v>
       </c>
       <c r="D279" s="13">
-        <v>8.0299999999999994</v>
+        <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B280" s="8" t="s">
         <v>15</v>
@@ -4441,12 +4441,12 @@
         <v>16</v>
       </c>
       <c r="D280" s="13">
-        <v>8.24</v>
+        <v>8.0299999999999994</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B281" s="8" t="s">
         <v>15</v>
@@ -4455,12 +4455,12 @@
         <v>16</v>
       </c>
       <c r="D281" s="13">
-        <v>8.26</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B282" s="8" t="s">
         <v>15</v>
@@ -4468,13 +4468,13 @@
       <c r="C282" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D282">
-        <v>7.9</v>
+      <c r="D282" s="13">
+        <v>8.26</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B283" s="8" t="s">
         <v>15</v>
@@ -4483,12 +4483,12 @@
         <v>16</v>
       </c>
       <c r="D283">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B284" s="8" t="s">
         <v>15</v>
@@ -4497,12 +4497,12 @@
         <v>16</v>
       </c>
       <c r="D284">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B285" s="8" t="s">
         <v>15</v>
@@ -4510,13 +4510,13 @@
       <c r="C285" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D285" s="13">
-        <v>8.1</v>
+      <c r="D285">
+        <v>7.9</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B286" s="8" t="s">
         <v>15</v>
@@ -4524,13 +4524,13 @@
       <c r="C286" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D286">
-        <v>7.62</v>
+      <c r="D286" s="13">
+        <v>8.1</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B287" s="8" t="s">
         <v>15</v>
@@ -4539,12 +4539,12 @@
         <v>16</v>
       </c>
       <c r="D287">
-        <v>8.8000000000000007</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B288" s="8" t="s">
         <v>15</v>
@@ -4553,12 +4553,12 @@
         <v>16</v>
       </c>
       <c r="D288">
-        <v>8.2200000000000006</v>
+        <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B289" s="8" t="s">
         <v>15</v>
@@ -4566,13 +4566,13 @@
       <c r="C289" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D289" s="13">
-        <v>8</v>
+      <c r="D289">
+        <v>8.2200000000000006</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B290" s="8" t="s">
         <v>15</v>
@@ -4581,12 +4581,12 @@
         <v>16</v>
       </c>
       <c r="D290" s="13">
-        <v>8.0500000000000007</v>
+        <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B291" s="8" t="s">
         <v>15</v>
@@ -4595,26 +4595,26 @@
         <v>16</v>
       </c>
       <c r="D291" s="13">
-        <v>8.1</v>
+        <v>8.0500000000000007</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" s="8">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B292" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C292" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D292" s="13" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="D292" s="13">
+        <v>8.1</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B293" s="8" t="s">
         <v>15</v>
@@ -4628,7 +4628,7 @@
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B294" s="8" t="s">
         <v>15</v>
@@ -4642,7 +4642,7 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B295" s="8" t="s">
         <v>15</v>
@@ -4656,7 +4656,7 @@
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B296" s="8" t="s">
         <v>15</v>
@@ -4670,7 +4670,7 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B297" s="8" t="s">
         <v>15</v>
@@ -4684,7 +4684,7 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B298" s="8" t="s">
         <v>15</v>
@@ -4698,7 +4698,7 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B299" s="8" t="s">
         <v>15</v>
@@ -4712,7 +4712,7 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B300" s="8" t="s">
         <v>15</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B301" s="8" t="s">
         <v>15</v>
@@ -4740,7 +4740,7 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A302" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B302" s="8" t="s">
         <v>15</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B303" s="8" t="s">
         <v>15</v>
@@ -4768,7 +4768,7 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B304" s="8" t="s">
         <v>15</v>
@@ -4782,7 +4782,7 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B305" s="8" t="s">
         <v>15</v>
@@ -4796,7 +4796,7 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B306" s="8" t="s">
         <v>15</v>
@@ -4810,7 +4810,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B307" s="8" t="s">
         <v>15</v>
@@ -4824,7 +4824,7 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B308" s="8" t="s">
         <v>15</v>
@@ -4838,7 +4838,7 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B309" s="8" t="s">
         <v>15</v>
@@ -4852,21 +4852,21 @@
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" s="8">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B310" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C310" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D310" s="13">
-        <v>98.1</v>
+        <v>17</v>
+      </c>
+      <c r="D310" s="13" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B311" s="8" t="s">
         <v>15</v>
@@ -4875,12 +4875,12 @@
         <v>18</v>
       </c>
       <c r="D311" s="13">
-        <v>114.4</v>
+        <v>98.1</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B312" s="8" t="s">
         <v>15</v>
@@ -4889,12 +4889,12 @@
         <v>18</v>
       </c>
       <c r="D312" s="13">
-        <v>128.4</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B313" s="8" t="s">
         <v>15</v>
@@ -4903,12 +4903,12 @@
         <v>18</v>
       </c>
       <c r="D313" s="13">
-        <v>130.6</v>
+        <v>128.4</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B314" s="8" t="s">
         <v>15</v>
@@ -4917,12 +4917,12 @@
         <v>18</v>
       </c>
       <c r="D314" s="13">
-        <v>99.6</v>
+        <v>130.6</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B315" s="8" t="s">
         <v>15</v>
@@ -4931,12 +4931,12 @@
         <v>18</v>
       </c>
       <c r="D315" s="13">
-        <v>96.56</v>
+        <v>99.6</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B316" s="8" t="s">
         <v>15</v>
@@ -4945,12 +4945,12 @@
         <v>18</v>
       </c>
       <c r="D316" s="13">
-        <v>100.9</v>
+        <v>96.56</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B317" s="8" t="s">
         <v>15</v>
@@ -4959,12 +4959,12 @@
         <v>18</v>
       </c>
       <c r="D317" s="13">
-        <v>106.19</v>
+        <v>100.9</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B318" s="8" t="s">
         <v>15</v>
@@ -4973,12 +4973,12 @@
         <v>18</v>
       </c>
       <c r="D318" s="13">
-        <v>106.08</v>
+        <v>106.19</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B319" s="8" t="s">
         <v>15</v>
@@ -4987,12 +4987,12 @@
         <v>18</v>
       </c>
       <c r="D319" s="13">
-        <v>104.04</v>
+        <v>106.08</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B320" s="8" t="s">
         <v>15</v>
@@ -5000,13 +5000,13 @@
       <c r="C320" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D320">
-        <v>91.15</v>
+      <c r="D320" s="13">
+        <v>104.04</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B321" s="8" t="s">
         <v>15</v>
@@ -5015,12 +5015,12 @@
         <v>18</v>
       </c>
       <c r="D321">
-        <v>109.7</v>
+        <v>91.15</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B322" s="8" t="s">
         <v>15</v>
@@ -5029,12 +5029,12 @@
         <v>18</v>
       </c>
       <c r="D322">
-        <v>103.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B323" s="8" t="s">
         <v>15</v>
@@ -5043,12 +5043,12 @@
         <v>18</v>
       </c>
       <c r="D323">
-        <v>103.78</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B324" s="8" t="s">
         <v>15</v>
@@ -5057,12 +5057,12 @@
         <v>18</v>
       </c>
       <c r="D324">
-        <v>110.9</v>
+        <v>103.78</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B325" s="8" t="s">
         <v>15</v>
@@ -5071,12 +5071,12 @@
         <v>18</v>
       </c>
       <c r="D325">
-        <v>95.96</v>
+        <v>110.9</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B326" s="8" t="s">
         <v>15</v>
@@ -5085,12 +5085,12 @@
         <v>18</v>
       </c>
       <c r="D326">
-        <v>106.26</v>
+        <v>95.96</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B327" s="8" t="s">
         <v>15</v>
@@ -5099,26 +5099,26 @@
         <v>18</v>
       </c>
       <c r="D327">
-        <v>108.36</v>
+        <v>106.26</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328" s="8">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B328" s="8" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C328" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D328" s="13">
-        <v>11.2</v>
+        <v>18</v>
+      </c>
+      <c r="D328">
+        <v>108.36</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B329" s="8" t="s">
         <v>20</v>
@@ -5126,13 +5126,13 @@
       <c r="C329" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D329">
-        <v>11.34</v>
+      <c r="D329" s="13">
+        <v>11.2</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B330" s="8" t="s">
         <v>20</v>
@@ -5146,7 +5146,7 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B331" s="8" t="s">
         <v>20</v>
@@ -5154,13 +5154,13 @@
       <c r="C331" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D331" s="13">
-        <v>11.31</v>
+      <c r="D331">
+        <v>11.34</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B332" s="8" t="s">
         <v>20</v>
@@ -5168,13 +5168,13 @@
       <c r="C332" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D332" s="14">
-        <v>11.33</v>
+      <c r="D332" s="13">
+        <v>11.31</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B333" s="8" t="s">
         <v>20</v>
@@ -5182,13 +5182,13 @@
       <c r="C333" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D333" s="13">
-        <v>11.28</v>
+      <c r="D333" s="14">
+        <v>11.33</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B334" s="8" t="s">
         <v>20</v>
@@ -5197,12 +5197,12 @@
         <v>16</v>
       </c>
       <c r="D334" s="13">
-        <v>11.24</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B335" s="8" t="s">
         <v>20</v>
@@ -5211,12 +5211,12 @@
         <v>16</v>
       </c>
       <c r="D335" s="13">
-        <v>11.25</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B336" s="8" t="s">
         <v>20</v>
@@ -5224,13 +5224,13 @@
       <c r="C336" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D336">
-        <v>11.28</v>
+      <c r="D336" s="13">
+        <v>11.25</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B337" s="8" t="s">
         <v>20</v>
@@ -5239,12 +5239,12 @@
         <v>16</v>
       </c>
       <c r="D337">
-        <v>11.14</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B338" s="8" t="s">
         <v>20</v>
@@ -5252,13 +5252,13 @@
       <c r="C338" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D338" s="13">
-        <v>11.31</v>
+      <c r="D338">
+        <v>11.14</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B339" s="8" t="s">
         <v>20</v>
@@ -5266,13 +5266,13 @@
       <c r="C339" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D339">
-        <v>11.22</v>
+      <c r="D339" s="13">
+        <v>11.31</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B340" s="8" t="s">
         <v>20</v>
@@ -5281,12 +5281,12 @@
         <v>16</v>
       </c>
       <c r="D340">
-        <v>11.29</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B341" s="8" t="s">
         <v>20</v>
@@ -5295,12 +5295,12 @@
         <v>16</v>
       </c>
       <c r="D341">
-        <v>11.39</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B342" s="8" t="s">
         <v>20</v>
@@ -5309,12 +5309,12 @@
         <v>16</v>
       </c>
       <c r="D342">
-        <v>11.29</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B343" s="8" t="s">
         <v>20</v>
@@ -5323,12 +5323,12 @@
         <v>16</v>
       </c>
       <c r="D343">
-        <v>11.43</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B344" s="8" t="s">
         <v>20</v>
@@ -5337,12 +5337,12 @@
         <v>16</v>
       </c>
       <c r="D344">
-        <v>11.35</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B345" s="8" t="s">
         <v>20</v>
@@ -5351,26 +5351,26 @@
         <v>16</v>
       </c>
       <c r="D345">
-        <v>11.48</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A346" s="8">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B346" s="8" t="s">
         <v>20</v>
       </c>
       <c r="C346" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D346" s="13">
-        <v>3</v>
+        <v>16</v>
+      </c>
+      <c r="D346">
+        <v>11.48</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A347" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B347" s="8" t="s">
         <v>20</v>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B348" s="8" t="s">
         <v>20</v>
@@ -5398,7 +5398,7 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A349" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B349" s="8" t="s">
         <v>20</v>
@@ -5412,7 +5412,7 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A350" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B350" s="8" t="s">
         <v>20</v>
@@ -5426,7 +5426,7 @@
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A351" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B351" s="8" t="s">
         <v>20</v>
@@ -5440,7 +5440,7 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A352" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B352" s="8" t="s">
         <v>20</v>
@@ -5454,7 +5454,7 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A353" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B353" s="8" t="s">
         <v>20</v>
@@ -5468,7 +5468,7 @@
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A354" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B354" s="8" t="s">
         <v>20</v>
@@ -5482,7 +5482,7 @@
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A355" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B355" s="8" t="s">
         <v>20</v>
@@ -5496,7 +5496,7 @@
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A356" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B356" s="8" t="s">
         <v>20</v>
@@ -5510,7 +5510,7 @@
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A357" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B357" s="8" t="s">
         <v>20</v>
@@ -5519,12 +5519,12 @@
         <v>17</v>
       </c>
       <c r="D357" s="13">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A358" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B358" s="8" t="s">
         <v>20</v>
@@ -5533,12 +5533,12 @@
         <v>17</v>
       </c>
       <c r="D358" s="13">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A359" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B359" s="8" t="s">
         <v>20</v>
@@ -5547,12 +5547,12 @@
         <v>17</v>
       </c>
       <c r="D359" s="13">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A360" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B360" s="8" t="s">
         <v>20</v>
@@ -5561,12 +5561,12 @@
         <v>17</v>
       </c>
       <c r="D360" s="13">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A361" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B361" s="8" t="s">
         <v>20</v>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A362" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B362" s="8" t="s">
         <v>20</v>
@@ -5594,7 +5594,7 @@
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A363" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B363" s="8" t="s">
         <v>20</v>
@@ -5608,21 +5608,21 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A364" s="8">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B364" s="8" t="s">
         <v>20</v>
       </c>
       <c r="C364" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D364" s="7">
-        <v>1945</v>
+        <v>17</v>
+      </c>
+      <c r="D364" s="13">
+        <v>3</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A365" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B365" s="8" t="s">
         <v>20</v>
@@ -5631,12 +5631,12 @@
         <v>18</v>
       </c>
       <c r="D365" s="7">
-        <v>1845</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A366" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B366" s="8" t="s">
         <v>20</v>
@@ -5645,12 +5645,12 @@
         <v>18</v>
       </c>
       <c r="D366" s="7">
-        <v>2166</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B367" s="8" t="s">
         <v>20</v>
@@ -5659,12 +5659,12 @@
         <v>18</v>
       </c>
       <c r="D367" s="7">
-        <v>1783</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A368" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B368" s="8" t="s">
         <v>20</v>
@@ -5673,12 +5673,12 @@
         <v>18</v>
       </c>
       <c r="D368" s="7">
-        <v>1772</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A369" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B369" s="8" t="s">
         <v>20</v>
@@ -5687,12 +5687,12 @@
         <v>18</v>
       </c>
       <c r="D369" s="7">
-        <v>1738</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A370" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B370" s="8" t="s">
         <v>20</v>
@@ -5701,12 +5701,12 @@
         <v>18</v>
       </c>
       <c r="D370" s="7">
-        <v>1639</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A371" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B371" s="8" t="s">
         <v>20</v>
@@ -5715,12 +5715,12 @@
         <v>18</v>
       </c>
       <c r="D371" s="7">
-        <v>1620</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A372" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B372" s="8" t="s">
         <v>20</v>
@@ -5729,12 +5729,12 @@
         <v>18</v>
       </c>
       <c r="D372" s="7">
-        <v>1865</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A373" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B373" s="8" t="s">
         <v>20</v>
@@ -5743,12 +5743,12 @@
         <v>18</v>
       </c>
       <c r="D373" s="7">
-        <v>1747</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A374" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B374" s="8" t="s">
         <v>20</v>
@@ -5757,12 +5757,12 @@
         <v>18</v>
       </c>
       <c r="D374" s="7">
-        <v>1925</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A375" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B375" s="8" t="s">
         <v>20</v>
@@ -5771,12 +5771,12 @@
         <v>18</v>
       </c>
       <c r="D375" s="7">
-        <v>1752</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A376" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B376" s="8" t="s">
         <v>20</v>
@@ -5785,12 +5785,12 @@
         <v>18</v>
       </c>
       <c r="D376" s="7">
-        <v>1742</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A377" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B377" s="8" t="s">
         <v>20</v>
@@ -5799,12 +5799,12 @@
         <v>18</v>
       </c>
       <c r="D377" s="7">
-        <v>1879</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A378" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B378" s="8" t="s">
         <v>20</v>
@@ -5813,12 +5813,12 @@
         <v>18</v>
       </c>
       <c r="D378" s="7">
-        <v>1561</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A379" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B379" s="8" t="s">
         <v>20</v>
@@ -5827,12 +5827,12 @@
         <v>18</v>
       </c>
       <c r="D379" s="7">
-        <v>1866</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A380" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B380" s="8" t="s">
         <v>20</v>
@@ -5841,12 +5841,12 @@
         <v>18</v>
       </c>
       <c r="D380" s="7">
-        <v>1652</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A381" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B381" s="8" t="s">
         <v>20</v>
@@ -5855,26 +5855,26 @@
         <v>18</v>
       </c>
       <c r="D381" s="7">
-        <v>1884</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A382" s="8">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B382" s="8" t="s">
         <v>20</v>
       </c>
       <c r="C382" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D382" s="13">
-        <v>36.51</v>
+        <v>18</v>
+      </c>
+      <c r="D382" s="7">
+        <v>1884</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A383" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B383" s="8" t="s">
         <v>20</v>
@@ -5882,13 +5882,13 @@
       <c r="C383" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D383">
-        <v>35.520000000000003</v>
+      <c r="D383" s="13">
+        <v>36.51</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A384" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B384" s="8" t="s">
         <v>20</v>
@@ -5897,12 +5897,12 @@
         <v>21</v>
       </c>
       <c r="D384">
-        <v>42.47</v>
+        <v>35.520000000000003</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A385" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B385" s="8" t="s">
         <v>20</v>
@@ -5910,13 +5910,13 @@
       <c r="C385" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D385" s="13">
-        <v>41.28</v>
+      <c r="D385">
+        <v>42.47</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A386" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B386" s="8" t="s">
         <v>20</v>
@@ -5925,12 +5925,12 @@
         <v>21</v>
       </c>
       <c r="D386" s="13">
-        <v>47.23</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A387" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B387" s="8" t="s">
         <v>20</v>
@@ -5939,12 +5939,12 @@
         <v>21</v>
       </c>
       <c r="D387" s="13">
-        <v>39.96</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A388" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B388" s="8" t="s">
         <v>20</v>
@@ -5953,12 +5953,12 @@
         <v>21</v>
       </c>
       <c r="D388" s="13">
-        <v>37.94</v>
+        <v>39.96</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A389" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B389" s="8" t="s">
         <v>20</v>
@@ -5967,12 +5967,12 @@
         <v>21</v>
       </c>
       <c r="D389" s="13">
-        <v>44.13</v>
+        <v>37.94</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A390" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B390" s="8" t="s">
         <v>20</v>
@@ -5980,13 +5980,13 @@
       <c r="C390" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D390">
-        <v>47.33</v>
+      <c r="D390" s="13">
+        <v>44.13</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A391" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B391" s="8" t="s">
         <v>20</v>
@@ -5995,12 +5995,12 @@
         <v>21</v>
       </c>
       <c r="D391">
-        <v>34.92</v>
+        <v>47.33</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A392" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B392" s="8" t="s">
         <v>20</v>
@@ -6009,12 +6009,12 @@
         <v>21</v>
       </c>
       <c r="D392">
-        <v>46.83</v>
+        <v>34.92</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A393" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B393" s="8" t="s">
         <v>20</v>
@@ -6022,13 +6022,13 @@
       <c r="C393" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D393" s="13">
-        <v>36.159999999999997</v>
+      <c r="D393">
+        <v>46.83</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A394" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B394" s="8" t="s">
         <v>20</v>
@@ -6037,12 +6037,12 @@
         <v>21</v>
       </c>
       <c r="D394" s="13">
-        <v>37.380000000000003</v>
+        <v>36.159999999999997</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A395" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B395" s="8" t="s">
         <v>20</v>
@@ -6050,13 +6050,13 @@
       <c r="C395" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D395">
-        <v>42.18</v>
+      <c r="D395" s="13">
+        <v>37.380000000000003</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A396" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B396" s="8" t="s">
         <v>20</v>
@@ -6065,12 +6065,12 @@
         <v>21</v>
       </c>
       <c r="D396">
-        <v>42.69</v>
+        <v>42.18</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A397" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B397" s="8" t="s">
         <v>20</v>
@@ -6078,13 +6078,13 @@
       <c r="C397" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D397" s="13">
-        <v>40.4</v>
+      <c r="D397">
+        <v>42.69</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A398" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B398" s="8" t="s">
         <v>20</v>
@@ -6093,12 +6093,12 @@
         <v>21</v>
       </c>
       <c r="D398" s="13">
-        <v>33.92</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A399" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B399" s="8" t="s">
         <v>20</v>
@@ -6107,26 +6107,26 @@
         <v>21</v>
       </c>
       <c r="D399" s="13">
-        <v>40.119999999999997</v>
+        <v>33.92</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A400" s="8">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B400" s="8" t="s">
         <v>20</v>
       </c>
       <c r="C400" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D400" s="13">
-        <v>5.07</v>
+        <v>40.119999999999997</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A401" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B401" s="8" t="s">
         <v>20</v>
@@ -6134,13 +6134,13 @@
       <c r="C401" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D401">
-        <v>5.05</v>
+      <c r="D401" s="13">
+        <v>5.07</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A402" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B402" s="8" t="s">
         <v>20</v>
@@ -6148,13 +6148,13 @@
       <c r="C402" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D402" s="13">
-        <v>5.0999999999999996</v>
+      <c r="D402">
+        <v>5.05</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A403" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B403" s="8" t="s">
         <v>20</v>
@@ -6163,12 +6163,12 @@
         <v>22</v>
       </c>
       <c r="D403" s="13">
-        <v>5.12</v>
+        <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A404" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B404" s="8" t="s">
         <v>20</v>
@@ -6177,12 +6177,12 @@
         <v>22</v>
       </c>
       <c r="D404" s="13">
-        <v>5.0599999999999996</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A405" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B405" s="8" t="s">
         <v>20</v>
@@ -6191,12 +6191,12 @@
         <v>22</v>
       </c>
       <c r="D405" s="13">
-        <v>5.5</v>
+        <v>5.0599999999999996</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B406" s="8" t="s">
         <v>20</v>
@@ -6205,12 +6205,12 @@
         <v>22</v>
       </c>
       <c r="D406" s="13">
-        <v>5.41</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A407" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B407" s="8" t="s">
         <v>20</v>
@@ -6219,12 +6219,12 @@
         <v>22</v>
       </c>
       <c r="D407" s="13">
-        <v>5.0599999999999996</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A408" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B408" s="8" t="s">
         <v>20</v>
@@ -6233,12 +6233,12 @@
         <v>22</v>
       </c>
       <c r="D408" s="13">
-        <v>5.0199999999999996</v>
+        <v>5.0599999999999996</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A409" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B409" s="8" t="s">
         <v>20</v>
@@ -6247,12 +6247,12 @@
         <v>22</v>
       </c>
       <c r="D409" s="13">
-        <v>5.61</v>
+        <v>5.0199999999999996</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A410" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B410" s="8" t="s">
         <v>20</v>
@@ -6261,12 +6261,12 @@
         <v>22</v>
       </c>
       <c r="D410" s="13">
-        <v>5.0999999999999996</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A411" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B411" s="8" t="s">
         <v>20</v>
@@ -6275,12 +6275,12 @@
         <v>22</v>
       </c>
       <c r="D411" s="13">
-        <v>5.05</v>
+        <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A412" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B412" s="8" t="s">
         <v>20</v>
@@ -6289,12 +6289,12 @@
         <v>22</v>
       </c>
       <c r="D412" s="13">
-        <v>3.03</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A413" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B413" s="8" t="s">
         <v>20</v>
@@ -6302,13 +6302,13 @@
       <c r="C413" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D413">
-        <v>4.08</v>
+      <c r="D413" s="13">
+        <v>3.03</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A414" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B414" s="8" t="s">
         <v>20</v>
@@ -6316,13 +6316,13 @@
       <c r="C414" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D414" s="13">
-        <v>4.71</v>
+      <c r="D414">
+        <v>4.08</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A415" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B415" s="8" t="s">
         <v>20</v>
@@ -6330,13 +6330,13 @@
       <c r="C415" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D415">
-        <v>4.0599999999999996</v>
+      <c r="D415" s="13">
+        <v>4.71</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A416" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B416" s="8" t="s">
         <v>20</v>
@@ -6344,13 +6344,13 @@
       <c r="C416" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D416" s="13">
-        <v>3.36</v>
+      <c r="D416">
+        <v>4.0599999999999996</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A417" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B417" s="8" t="s">
         <v>20</v>
@@ -6358,7 +6358,21 @@
       <c r="C417" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D417">
+      <c r="D417" s="13">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A418" s="8">
+        <v>19</v>
+      </c>
+      <c r="B418" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C418" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D418">
         <v>4.0199999999999996</v>
       </c>
     </row>
